--- a/output/turkey_generation_mix_dashboard_daily.xlsx
+++ b/output/turkey_generation_mix_dashboard_daily.xlsx
@@ -654,40 +654,40 @@
         <v>46295</v>
       </c>
       <c r="B2" t="n">
-        <v>821.4431578947367</v>
+        <v>845.441304347826</v>
       </c>
       <c r="C2" t="n">
-        <v>1201.221052631579</v>
+        <v>1014.253043478261</v>
       </c>
       <c r="D2" t="n">
-        <v>1133.901578947369</v>
+        <v>1144.379565217391</v>
       </c>
       <c r="E2" t="n">
-        <v>61.18315789473684</v>
+        <v>65.36652173913043</v>
       </c>
       <c r="F2" t="n">
-        <v>2136.593684210526</v>
+        <v>2260.416956521739</v>
       </c>
       <c r="G2" t="n">
-        <v>8659.079473684211</v>
+        <v>8939.307826086957</v>
       </c>
       <c r="H2" t="n">
-        <v>11210.39789473684</v>
+        <v>11875.11956521739</v>
       </c>
       <c r="I2" t="n">
-        <v>9732.176842105264</v>
+        <v>10624.66956521739</v>
       </c>
       <c r="J2" t="n">
-        <v>88.80315789473686</v>
+        <v>88.72260869565217</v>
       </c>
       <c r="K2" t="n">
-        <v>35044.8</v>
+        <v>36857.67695652174</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6148650329082535</v>
+        <v>0.6123025965789889</v>
       </c>
       <c r="M2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
